--- a/questionnaire_templates/005_workforce_agility_benchmark_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/005_workforce_agility_benchmark_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mostly_agile</t>
+          <t>Mostly agile</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mostly_inflexible</t>
+          <t>Mostly inflexible</t>
         </is>
       </c>
     </row>
